--- a/workbooks/urbanization-ru-mx.xlsx
+++ b/workbooks/urbanization-ru-mx.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\WINAPPS\SLOVO\UKR\github\RTSS\workbooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61C0C447-8905-479D-97E6-1F58F050EBA5}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{976A2D7B-B4ED-42A4-8846-5EF5BD732348}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-60" yWindow="-60" windowWidth="38520" windowHeight="23700" firstSheet="3" activeTab="13" xr2:uid="{9806A3BC-D491-4476-99E9-37D3951075C7}"/>
+    <workbookView xWindow="21795" yWindow="960" windowWidth="16380" windowHeight="15630" activeTab="2" xr2:uid="{9806A3BC-D491-4476-99E9-37D3951075C7}"/>
   </bookViews>
   <sheets>
     <sheet name="Notes" sheetId="1" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="666" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="671" uniqueCount="156">
   <si>
     <t>от</t>
   </si>
@@ -502,6 +502,21 @@
   </si>
   <si>
     <t>"Séptimo Censo General de Población 6 de junio de 1950. Secretaría de Economía Dirección General de Estadística. Resumen General", стр. 119</t>
+  </si>
+  <si>
+    <t>https://www.istmat.org/files/uploads/44830/rgae_4372.92.161_l.1-34.pdf</t>
+  </si>
+  <si>
+    <t>См. подробнее в urbanization-ru-1897.xlsx</t>
+  </si>
+  <si>
+    <t>https://www.istmat.org/node/44830</t>
+  </si>
+  <si>
+    <t>РГАЭ Ф.4372, Оп.92, Д.161, Л.1-34</t>
+  </si>
+  <si>
+    <t>"В 1926 году некоторые города были переписаны с пригородами и слободами, не входящими в городскую черту"</t>
   </si>
 </sst>
 </file>
@@ -717,12 +732,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -736,6 +745,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="7">
     <cellStyle name="Comma 2" xfId="5" xr:uid="{2A5730CF-2000-4C9F-A914-E035B50DA721}"/>
@@ -1301,22 +1316,22 @@
       <c r="J2" s="7"/>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="C3" s="29" t="s">
+      <c r="C3" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="D3" s="29"/>
-      <c r="I3" s="29" t="s">
+      <c r="D3" s="36"/>
+      <c r="I3" s="36" t="s">
         <v>44</v>
       </c>
-      <c r="J3" s="29"/>
-      <c r="O3" s="29" t="s">
+      <c r="J3" s="36"/>
+      <c r="O3" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="P3" s="29"/>
-      <c r="U3" s="29" t="s">
+      <c r="P3" s="36"/>
+      <c r="U3" s="36" t="s">
         <v>44</v>
       </c>
-      <c r="V3" s="29"/>
+      <c r="V3" s="36"/>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
@@ -3244,7 +3259,7 @@
       <c r="A5" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="33" t="s">
+      <c r="B5" s="31" t="s">
         <v>1</v>
       </c>
       <c r="C5" s="27" t="s">
@@ -3256,7 +3271,7 @@
       <c r="I5" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="J5" s="33" t="s">
+      <c r="J5" s="31" t="s">
         <v>1</v>
       </c>
       <c r="K5" s="27" t="s">
@@ -3693,7 +3708,7 @@
       <c r="A25" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="L25" s="34"/>
+      <c r="L25" s="32"/>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
@@ -3704,7 +3719,7 @@
         <v>14853457</v>
       </c>
       <c r="J26" s="2"/>
-      <c r="L26" s="35"/>
+      <c r="L26" s="33"/>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
@@ -3715,16 +3730,16 @@
         <v>57.604335274451415</v>
       </c>
       <c r="J27" s="2"/>
-      <c r="L27" s="36"/>
+      <c r="L27" s="34"/>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="L28" s="34"/>
+      <c r="L28" s="32"/>
     </row>
     <row r="29" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A29" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="L29" s="34"/>
+      <c r="L29" s="32"/>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
@@ -3735,7 +3750,7 @@
         <v>11807819</v>
       </c>
       <c r="J30" s="2"/>
-      <c r="L30" s="35"/>
+      <c r="L30" s="33"/>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
@@ -3746,16 +3761,16 @@
         <v>45.792812039381644</v>
       </c>
       <c r="J31" s="2"/>
-      <c r="L31" s="36"/>
+      <c r="L31" s="34"/>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="L32" s="34"/>
+      <c r="L32" s="32"/>
     </row>
     <row r="33" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A33" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="L33" s="34"/>
+      <c r="L33" s="32"/>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
@@ -3766,7 +3781,7 @@
         <v>10995012</v>
       </c>
       <c r="J34" s="2"/>
-      <c r="L34" s="35"/>
+      <c r="L34" s="33"/>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
@@ -3777,16 +3792,16 @@
         <v>42.640602628372406</v>
       </c>
       <c r="J35" s="2"/>
-      <c r="L35" s="36"/>
+      <c r="L35" s="34"/>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="L36" s="34"/>
+      <c r="L36" s="32"/>
     </row>
     <row r="37" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A37" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="L37" s="34"/>
+      <c r="L37" s="32"/>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
@@ -3797,7 +3812,7 @@
         <v>8871877</v>
       </c>
       <c r="J38" s="2"/>
-      <c r="L38" s="35"/>
+      <c r="L38" s="33"/>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
@@ -3808,16 +3823,16 @@
         <v>34.406709308256936</v>
       </c>
       <c r="J39" s="2"/>
-      <c r="L39" s="36"/>
+      <c r="L39" s="34"/>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="L40" s="34"/>
+      <c r="L40" s="32"/>
     </row>
     <row r="41" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A41" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="L41" s="34"/>
+      <c r="L41" s="32"/>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
@@ -3828,7 +3843,7 @@
         <v>6118181</v>
       </c>
       <c r="J42" s="2"/>
-      <c r="L42" s="35"/>
+      <c r="L42" s="33"/>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
@@ -3839,16 +3854,16 @@
         <v>23.727388822263961</v>
       </c>
       <c r="J43" s="2"/>
-      <c r="L43" s="36"/>
+      <c r="L43" s="34"/>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="L44" s="34"/>
+      <c r="L44" s="32"/>
     </row>
     <row r="45" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A45" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="L45" s="34"/>
+      <c r="L45" s="32"/>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
@@ -3859,7 +3874,7 @@
         <v>3953551</v>
       </c>
       <c r="J46" s="2"/>
-      <c r="L46" s="35"/>
+      <c r="L46" s="33"/>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
@@ -3870,19 +3885,19 @@
         <v>15.332570547626903</v>
       </c>
       <c r="J47" s="2"/>
-      <c r="L47" s="36"/>
+      <c r="L47" s="34"/>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="L48" s="34"/>
+      <c r="L48" s="32"/>
     </row>
     <row r="49" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L49" s="34"/>
+      <c r="L49" s="32"/>
     </row>
     <row r="50" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L50" s="34"/>
+      <c r="L50" s="32"/>
     </row>
     <row r="51" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L51" s="34"/>
+      <c r="L51" s="32"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6670,17 +6685,17 @@
       </c>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="C41" s="29" t="s">
+      <c r="C41" s="36" t="s">
         <v>37</v>
       </c>
-      <c r="D41" s="29"/>
-      <c r="E41" s="29"/>
+      <c r="D41" s="36"/>
+      <c r="E41" s="36"/>
       <c r="F41" s="2"/>
-      <c r="G41" s="29" t="s">
+      <c r="G41" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="H41" s="29"/>
-      <c r="I41" s="29"/>
+      <c r="H41" s="36"/>
+      <c r="I41" s="36"/>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
@@ -7030,7 +7045,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5985972A-1F2C-44A9-AD06-BDF66C69F9F0}">
-  <dimension ref="A3:O42"/>
+  <dimension ref="A3:O48"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="11.140625" bestFit="1" customWidth="1"/>
@@ -7117,27 +7132,27 @@
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A15" s="31" t="s">
+      <c r="A15" s="29" t="s">
         <v>2</v>
       </c>
       <c r="B15" s="1">
         <v>2000</v>
       </c>
       <c r="C15" s="27"/>
-      <c r="D15" s="32">
+      <c r="D15" s="30">
         <v>93768</v>
       </c>
-      <c r="E15" s="32">
+      <c r="E15" s="30">
         <v>67075</v>
       </c>
-      <c r="F15" s="32"/>
-      <c r="G15" s="32">
+      <c r="F15" s="30"/>
+      <c r="G15" s="30">
         <v>3524</v>
       </c>
-      <c r="H15" s="32">
+      <c r="H15" s="30">
         <v>14693</v>
       </c>
-      <c r="I15" s="32">
+      <c r="I15" s="30">
         <v>8476</v>
       </c>
       <c r="K15" s="1">
@@ -7178,7 +7193,7 @@
       <c r="I16" s="8">
         <v>36697</v>
       </c>
-      <c r="J16" s="30"/>
+      <c r="J16" s="28"/>
       <c r="K16" s="1">
         <f t="shared" ref="K16:K20" si="0">E16+H16</f>
         <v>544527</v>
@@ -7217,7 +7232,7 @@
       <c r="I17" s="8">
         <v>99955</v>
       </c>
-      <c r="J17" s="30"/>
+      <c r="J17" s="28"/>
       <c r="K17" s="1">
         <f t="shared" si="0"/>
         <v>1328953</v>
@@ -7257,7 +7272,7 @@
       <c r="I18" s="8">
         <v>143234</v>
       </c>
-      <c r="J18" s="30"/>
+      <c r="J18" s="28"/>
       <c r="K18" s="1">
         <f t="shared" si="0"/>
         <v>1770078</v>
@@ -7296,7 +7311,7 @@
       <c r="I19" s="8">
         <v>291836</v>
       </c>
-      <c r="J19" s="30"/>
+      <c r="J19" s="28"/>
       <c r="K19" s="1">
         <f t="shared" si="0"/>
         <v>2319081</v>
@@ -7335,7 +7350,7 @@
       <c r="I20" s="8">
         <v>354172</v>
       </c>
-      <c r="J20" s="30"/>
+      <c r="J20" s="28"/>
       <c r="K20" s="1">
         <f t="shared" si="0"/>
         <v>6435590</v>
@@ -7624,46 +7639,46 @@
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A33" s="31" t="s">
+      <c r="A33" s="29" t="s">
         <v>2</v>
       </c>
       <c r="B33" s="1">
         <v>2000</v>
       </c>
       <c r="D33" s="1">
-        <f>D15</f>
+        <f t="shared" ref="D33:I33" si="6">D15</f>
         <v>93768</v>
       </c>
       <c r="E33" s="1">
-        <f>E15</f>
+        <f t="shared" si="6"/>
         <v>67075</v>
       </c>
       <c r="F33" s="1">
-        <f>F15</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="G33" s="1">
-        <f>G15</f>
+        <f t="shared" si="6"/>
         <v>3524</v>
       </c>
       <c r="H33" s="1">
-        <f>H15</f>
+        <f t="shared" si="6"/>
         <v>14693</v>
       </c>
       <c r="I33" s="1">
-        <f>I15</f>
+        <f t="shared" si="6"/>
         <v>8476</v>
       </c>
       <c r="K33" s="1">
-        <f t="shared" ref="K33:K37" si="6">E33+H33</f>
+        <f t="shared" ref="K33:K37" si="7">E33+H33</f>
         <v>81768</v>
       </c>
       <c r="L33" s="1">
-        <f t="shared" ref="L33:L37" si="7">K33+G33</f>
+        <f t="shared" ref="L33:L37" si="8">K33+G33</f>
         <v>85292</v>
       </c>
       <c r="M33" s="1">
-        <f t="shared" ref="M33:M39" si="8">L33+I33</f>
+        <f t="shared" ref="M33:M39" si="9">L33+I33</f>
         <v>93768</v>
       </c>
     </row>
@@ -7675,39 +7690,39 @@
         <v>5000</v>
       </c>
       <c r="D34" s="1">
-        <f>D16+SUM(D24:D26)</f>
+        <f t="shared" ref="D34:I34" si="10">D16+SUM(D24:D26)</f>
         <v>16314026</v>
       </c>
       <c r="E34" s="1">
-        <f>E16+SUM(E24:E26)</f>
+        <f t="shared" si="10"/>
         <v>13039825</v>
       </c>
       <c r="F34" s="1">
-        <f>F16+SUM(F24:F26)</f>
+        <f t="shared" si="10"/>
         <v>621062</v>
       </c>
       <c r="G34" s="1">
-        <f>G16+SUM(G24:G26)</f>
+        <f t="shared" si="10"/>
         <v>1469351</v>
       </c>
       <c r="H34" s="1">
-        <f>H16+SUM(H24:H26)</f>
+        <f t="shared" si="10"/>
         <v>446219</v>
       </c>
       <c r="I34" s="1">
-        <f>I16+SUM(I24:I26)</f>
+        <f t="shared" si="10"/>
         <v>737569</v>
       </c>
       <c r="K34" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>13486044</v>
       </c>
       <c r="L34" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>14955395</v>
       </c>
       <c r="M34" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>15692964</v>
       </c>
     </row>
@@ -7719,39 +7734,39 @@
         <v>10000</v>
       </c>
       <c r="D35" s="1">
-        <f>D17+D27</f>
+        <f t="shared" ref="D35:I36" si="11">D17+D27</f>
         <v>7459768</v>
       </c>
       <c r="E35" s="1">
-        <f>E17+E27</f>
+        <f t="shared" si="11"/>
         <v>5509571</v>
       </c>
       <c r="F35" s="1">
-        <f>F17+F27</f>
+        <f t="shared" si="11"/>
         <v>526438</v>
       </c>
       <c r="G35" s="1">
-        <f>G17+G27</f>
+        <f t="shared" si="11"/>
         <v>1141946</v>
       </c>
       <c r="H35" s="1">
-        <f>H17+H27</f>
+        <f t="shared" si="11"/>
         <v>136181</v>
       </c>
       <c r="I35" s="1">
-        <f>I17+I27</f>
+        <f t="shared" si="11"/>
         <v>145632</v>
       </c>
       <c r="K35" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>5645752</v>
       </c>
       <c r="L35" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>6787698</v>
       </c>
       <c r="M35" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>6933330</v>
       </c>
     </row>
@@ -7763,39 +7778,39 @@
         <v>20000</v>
       </c>
       <c r="D36" s="1">
-        <f>D18+D28</f>
+        <f t="shared" si="11"/>
         <v>3481716</v>
       </c>
       <c r="E36" s="1">
-        <f>E18+E28</f>
+        <f t="shared" si="11"/>
         <v>2824047</v>
       </c>
       <c r="F36" s="1">
-        <f>F18+F28</f>
+        <f t="shared" si="11"/>
         <v>278451</v>
       </c>
       <c r="G36" s="1">
-        <f>G18+G28</f>
+        <f t="shared" si="11"/>
         <v>708953</v>
       </c>
       <c r="H36" s="1">
-        <f>H18+H28</f>
+        <f t="shared" si="11"/>
         <v>98312</v>
       </c>
       <c r="I36" s="1">
-        <f>I18+I28</f>
+        <f t="shared" si="11"/>
         <v>154208</v>
       </c>
       <c r="K36" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>2922359</v>
       </c>
       <c r="L36" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3631312</v>
       </c>
       <c r="M36" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>3785520</v>
       </c>
     </row>
@@ -7807,39 +7822,39 @@
         <v>131</v>
       </c>
       <c r="D37" s="1">
-        <f>SUM(D19:D20)+D29</f>
+        <f t="shared" ref="D37:I37" si="12">SUM(D19:D20)+D29</f>
         <v>11806368</v>
       </c>
       <c r="E37" s="1">
-        <f>SUM(E19:E20)+E29</f>
+        <f t="shared" si="12"/>
         <v>8761149</v>
       </c>
       <c r="F37" s="1">
-        <f>SUM(F19:F20)+F29</f>
+        <f t="shared" si="12"/>
         <v>1398191</v>
       </c>
       <c r="G37" s="1">
-        <f>SUM(G19:G20)+G29</f>
+        <f t="shared" si="12"/>
         <v>737829</v>
       </c>
       <c r="H37" s="1">
-        <f>SUM(H19:H20)+H29</f>
+        <f t="shared" si="12"/>
         <v>263191</v>
       </c>
       <c r="I37" s="1">
-        <f>SUM(I19:I20)+I29</f>
+        <f t="shared" si="12"/>
         <v>646008</v>
       </c>
       <c r="K37" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>9024340</v>
       </c>
       <c r="L37" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>9762169</v>
       </c>
       <c r="M37" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>10408177</v>
       </c>
     </row>
@@ -7877,7 +7892,7 @@
         <v>109383251</v>
       </c>
       <c r="M39" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>117130420</v>
       </c>
     </row>
@@ -7886,27 +7901,27 @@
         <v>143</v>
       </c>
       <c r="D41" s="3">
-        <f>SUM(D34:D37)/D39*100</f>
+        <f t="shared" ref="D41:I41" si="13">SUM(D34:D37)/D39*100</f>
         <v>30.857848416330253</v>
       </c>
       <c r="E41" s="3">
-        <f>SUM(E34:E37)/E39*100</f>
+        <f t="shared" si="13"/>
         <v>31.975044887692487</v>
       </c>
       <c r="F41" s="3">
-        <f>SUM(F34:F37)/F39*100</f>
+        <f t="shared" si="13"/>
         <v>29.865806270129191</v>
       </c>
       <c r="G41" s="3">
-        <f>SUM(G34:G37)/G39*100</f>
+        <f t="shared" si="13"/>
         <v>43.379769877900834</v>
       </c>
       <c r="H41" s="3">
-        <f>SUM(H34:H37)/H39*100</f>
+        <f t="shared" si="13"/>
         <v>16.318130441592551</v>
       </c>
       <c r="I41" s="3">
-        <f>SUM(I34:I37)/I39*100</f>
+        <f t="shared" si="13"/>
         <v>21.729447234209037</v>
       </c>
       <c r="K41" s="3">
@@ -7931,27 +7946,27 @@
         <v>144</v>
       </c>
       <c r="D42" s="3">
-        <f>D37/D39*100</f>
+        <f t="shared" ref="D42:I42" si="14">D37/D39*100</f>
         <v>9.3267178319335322</v>
       </c>
       <c r="E42" s="3">
-        <f>E37/E39*100</f>
+        <f t="shared" si="14"/>
         <v>9.296231140038735</v>
       </c>
       <c r="F42" s="3">
-        <f>F37/F39*100</f>
+        <f t="shared" si="14"/>
         <v>14.78611965497422</v>
       </c>
       <c r="G42" s="3">
-        <f>G37/G39*100</f>
+        <f t="shared" si="14"/>
         <v>7.8871929869383255</v>
       </c>
       <c r="H42" s="3">
-        <f>H37/H39*100</f>
+        <f t="shared" si="14"/>
         <v>4.5500279891611584</v>
       </c>
       <c r="I42" s="3">
-        <f>I37/I39*100</f>
+        <f t="shared" si="14"/>
         <v>8.3386331187560252</v>
       </c>
       <c r="K42" s="3">
@@ -7969,6 +7984,11 @@
       <c r="O42" s="3">
         <f>AVERAGE(K42:L42)</f>
         <v>8.973254587697479</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>152</v>
       </c>
     </row>
   </sheetData>
@@ -7978,7 +7998,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4D8DB8B-3990-447D-A504-5F100C779FB0}">
-  <dimension ref="A1:AG49"/>
+  <dimension ref="A1:AG56"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" bestFit="1" customWidth="1"/>
@@ -8006,40 +8026,40 @@
       <c r="Q1" s="19"/>
     </row>
     <row r="3" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A3" s="29" t="s">
+      <c r="A3" s="36" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="29"/>
-      <c r="C3" s="28" t="s">
+      <c r="B3" s="36"/>
+      <c r="C3" s="35" t="s">
         <v>37</v>
       </c>
-      <c r="D3" s="28"/>
-      <c r="E3" s="28" t="s">
+      <c r="D3" s="35"/>
+      <c r="E3" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="F3" s="28"/>
-      <c r="G3" s="28" t="s">
+      <c r="F3" s="35"/>
+      <c r="G3" s="35" t="s">
         <v>39</v>
       </c>
-      <c r="H3" s="28"/>
-      <c r="I3" s="28" t="s">
+      <c r="H3" s="35"/>
+      <c r="I3" s="35" t="s">
         <v>32</v>
       </c>
-      <c r="J3" s="28"/>
-      <c r="K3" s="28" t="s">
+      <c r="J3" s="35"/>
+      <c r="K3" s="35" t="s">
         <v>33</v>
       </c>
-      <c r="L3" s="28"/>
-      <c r="M3" s="28" t="s">
+      <c r="L3" s="35"/>
+      <c r="M3" s="35" t="s">
         <v>34</v>
       </c>
-      <c r="N3" s="28"/>
-      <c r="Q3" s="29"/>
-      <c r="R3" s="29"/>
-      <c r="S3" s="28"/>
-      <c r="T3" s="28"/>
-      <c r="U3" s="28"/>
-      <c r="V3" s="28"/>
+      <c r="N3" s="35"/>
+      <c r="Q3" s="36"/>
+      <c r="R3" s="36"/>
+      <c r="S3" s="35"/>
+      <c r="T3" s="35"/>
+      <c r="U3" s="35"/>
+      <c r="V3" s="35"/>
     </row>
     <row r="4" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
@@ -9096,7 +9116,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="49" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D49" s="12">
         <f>F19/D19*100</f>
         <v>17.905381557325782</v>
@@ -9104,6 +9124,26 @@
       <c r="J49" s="12">
         <f>L19/J19*100</f>
         <v>17.298887290155594</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>154</v>
       </c>
     </row>
   </sheetData>
@@ -9555,18 +9595,18 @@
       </c>
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="I3" s="29" t="s">
+      <c r="I3" s="36" t="s">
         <v>44</v>
       </c>
-      <c r="J3" s="29"/>
+      <c r="J3" s="36"/>
       <c r="M3" s="7"/>
       <c r="N3" s="7"/>
     </row>
     <row r="4" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="C4" s="29" t="s">
+      <c r="C4" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="D4" s="29"/>
+      <c r="D4" s="36"/>
       <c r="G4" s="7" t="s">
         <v>0</v>
       </c>
@@ -9579,14 +9619,14 @@
       <c r="J4" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="P4" s="29" t="s">
+      <c r="P4" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="Q4" s="29"/>
-      <c r="U4" s="29" t="s">
+      <c r="Q4" s="36"/>
+      <c r="U4" s="36" t="s">
         <v>44</v>
       </c>
-      <c r="V4" s="29"/>
+      <c r="V4" s="36"/>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
@@ -10200,22 +10240,22 @@
       <c r="J2" s="7"/>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="C3" s="29" t="s">
+      <c r="C3" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="D3" s="29"/>
-      <c r="I3" s="29" t="s">
+      <c r="D3" s="36"/>
+      <c r="I3" s="36" t="s">
         <v>44</v>
       </c>
-      <c r="J3" s="29"/>
-      <c r="P3" s="29" t="s">
+      <c r="J3" s="36"/>
+      <c r="P3" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="Q3" s="29"/>
-      <c r="U3" s="29" t="s">
+      <c r="Q3" s="36"/>
+      <c r="U3" s="36" t="s">
         <v>44</v>
       </c>
-      <c r="V3" s="29"/>
+      <c r="V3" s="36"/>
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
@@ -11769,16 +11809,16 @@
       </c>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="I2" s="29" t="s">
+      <c r="I2" s="36" t="s">
         <v>44</v>
       </c>
-      <c r="J2" s="29"/>
+      <c r="J2" s="36"/>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="C3" s="29" t="s">
+      <c r="C3" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="D3" s="29"/>
+      <c r="D3" s="36"/>
       <c r="G3" s="7" t="s">
         <v>0</v>
       </c>
@@ -11791,14 +11831,14 @@
       <c r="J3" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="O3" s="29" t="s">
+      <c r="O3" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="P3" s="29"/>
-      <c r="T3" s="29" t="s">
+      <c r="P3" s="36"/>
+      <c r="T3" s="36" t="s">
         <v>44</v>
       </c>
-      <c r="U3" s="29"/>
+      <c r="U3" s="36"/>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
